--- a/School_docs/Daffodils/STAFF INFO.xlsx
+++ b/School_docs/Daffodils/STAFF INFO.xlsx
@@ -1193,6 +1193,11 @@
           <t>KUMARI</t>
         </is>
       </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6203757534</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>OFFICE INCHARGE</t>
@@ -1213,6 +1218,11 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>KUMARI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>9304091054</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
